--- a/Deliverables/Bracelet(Aux_v2.0)/BOM/Bracelet_Aux_v2.0.xlsx
+++ b/Deliverables/Bracelet(Aux_v2.0)/BOM/Bracelet_Aux_v2.0.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="153222"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\GitHub\BrianPeri-SmartWatch\Deliverables\Bracelet(Aux_v2.0)\_Deliverables\BOM\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Github\BrianPeri-SmartWatch\Deliverables\Bracelet(Aux_v2.0)\BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -14,7 +14,7 @@
   <sheets>
     <sheet name="Bracelet_Aux_v2.0" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="152511"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="42">
   <si>
     <t>Description</t>
   </si>
@@ -38,9 +38,6 @@
     <t>0.1uF</t>
   </si>
   <si>
-    <t>Multilayer Ceramic Capacitors MLCC - SMD/SMT 0201 0.1uF 25volts X5R 10%</t>
-  </si>
-  <si>
     <t>C1, C2</t>
   </si>
   <si>
@@ -62,9 +59,6 @@
     <t>J1</t>
   </si>
   <si>
-    <t/>
-  </si>
-  <si>
     <t>SMD PADS</t>
   </si>
   <si>
@@ -138,15 +132,34 @@
   </si>
   <si>
     <t>Single Board Cost</t>
+  </si>
+  <si>
+    <t>Unit Cost (25 Boards)</t>
+  </si>
+  <si>
+    <t>Total Cost (25)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAP CER 0.1UF 25V X5R 0201
+</t>
+  </si>
+  <si>
+    <t>------</t>
+  </si>
+  <si>
+    <t>-----</t>
+  </si>
+  <si>
+    <t>Quantity 25</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="2">
-    <numFmt numFmtId="168" formatCode="&quot;$&quot;#,##0.00"/>
-    <numFmt numFmtId="171" formatCode="&quot;$&quot;#,##0.0000"/>
+    <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
+    <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0.0000"/>
   </numFmts>
   <fonts count="11" x14ac:knownFonts="1">
     <font>
@@ -259,7 +272,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="21">
+  <borders count="24">
     <border>
       <left/>
       <right/>
@@ -517,6 +530,41 @@
       </right>
       <top/>
       <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="medium">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
@@ -526,8 +574,83 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="14" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="17" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="17" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="19" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="11" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -537,75 +660,10 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="10" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="11" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="6" fillId="3" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="13" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="14" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="171" fontId="6" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="16" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="17" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="17" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -614,27 +672,27 @@
     <xf numFmtId="0" fontId="10" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="168" fontId="6" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="5" fillId="3" borderId="17" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="6" fillId="3" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="5" fillId="3" borderId="19" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="5" fillId="3" borderId="11" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="13" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="10" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="16" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -916,291 +974,342 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Q7"/>
+  <dimension ref="A1:T7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="6.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="7" width="14.42578125" customWidth="1"/>
-    <col min="13" max="13" width="11.5703125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="12.140625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="18.7109375" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="12.5703125" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.42578125" customWidth="1"/>
+    <col min="3" max="3" width="27.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.42578125" customWidth="1"/>
+    <col min="5" max="5" width="18.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="25.28515625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" customWidth="1"/>
+    <col min="10" max="10" width="19.42578125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="18.7109375" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="19.7109375" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="13.7109375" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:20" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="26" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1" s="27"/>
+      <c r="C1" s="27"/>
+      <c r="D1" s="27"/>
+      <c r="E1" s="27"/>
+      <c r="F1" s="27"/>
+      <c r="G1" s="27"/>
+      <c r="H1" s="27"/>
+      <c r="I1" s="27"/>
+      <c r="J1" s="27"/>
+      <c r="K1" s="27"/>
+      <c r="L1" s="27"/>
+      <c r="M1" s="27"/>
+      <c r="N1" s="27"/>
+      <c r="O1" s="27"/>
+      <c r="P1" s="27"/>
+      <c r="Q1" s="27"/>
+      <c r="R1" s="27"/>
+      <c r="S1" s="27"/>
+      <c r="T1" s="28"/>
+    </row>
+    <row r="2" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2"/>
-      <c r="I1" s="2"/>
-      <c r="J1" s="2"/>
-      <c r="K1" s="2"/>
-      <c r="L1" s="2"/>
-      <c r="M1" s="2"/>
-      <c r="N1" s="2"/>
-      <c r="O1" s="2"/>
-      <c r="P1" s="2"/>
-      <c r="Q1" s="3"/>
+      <c r="C2" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="M2" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="N2" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="O2" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="P2" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="Q2" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="R2" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="S2" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="T2" s="2" t="s">
+        <v>28</v>
+      </c>
     </row>
-    <row r="2" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="B2" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="C2" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="D2" s="5" t="s">
+    <row r="3" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="33">
         <v>1</v>
       </c>
-      <c r="E2" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="F2" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="G2" s="5" t="s">
+      <c r="B3" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="C3" s="38" t="s">
+        <v>38</v>
+      </c>
+      <c r="D3" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="E3" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="F3" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="G3" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="H3" s="39" t="s">
+        <v>39</v>
+      </c>
+      <c r="I3" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="J3" s="11">
         <v>2</v>
       </c>
-      <c r="H2" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="I2" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="J2" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="K2" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="L2" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="M2" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="N2" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="O2" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="P2" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="Q2" s="5" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="3" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="7">
-        <v>1</v>
-      </c>
-      <c r="B3" s="17" t="s">
-        <v>32</v>
-      </c>
-      <c r="C3" s="18" t="s">
-        <v>4</v>
-      </c>
-      <c r="D3" s="19" t="s">
-        <v>5</v>
-      </c>
-      <c r="E3" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="F3" s="19" t="s">
-        <v>7</v>
-      </c>
-      <c r="G3" s="19" t="s">
-        <v>8</v>
-      </c>
-      <c r="H3" s="20"/>
-      <c r="I3" s="19" t="s">
-        <v>3</v>
-      </c>
-      <c r="J3" s="21">
-        <v>2</v>
-      </c>
-      <c r="K3" s="20">
+      <c r="K3" s="10">
         <f>J3*5</f>
         <v>10</v>
       </c>
-      <c r="L3" s="22" t="s">
-        <v>31</v>
-      </c>
-      <c r="M3" s="23">
+      <c r="L3" s="10">
+        <f>J3*25</f>
+        <v>50</v>
+      </c>
+      <c r="M3" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="N3" s="13">
         <v>0.1</v>
       </c>
-      <c r="N3" s="33">
-        <f>M3*J3</f>
+      <c r="O3" s="19">
+        <f>N3*J3</f>
         <v>0.2</v>
       </c>
-      <c r="O3" s="23">
+      <c r="P3" s="13">
         <v>5.6000000000000001E-2</v>
       </c>
-      <c r="P3" s="33">
-        <f>O3*K3</f>
+      <c r="Q3" s="19">
+        <f>P3*K3</f>
         <v>0.56000000000000005</v>
       </c>
-      <c r="Q3" s="24"/>
+      <c r="R3" s="35">
+        <v>3.04E-2</v>
+      </c>
+      <c r="S3" s="35">
+        <f>R3*L3</f>
+        <v>1.52</v>
+      </c>
+      <c r="T3" s="14"/>
     </row>
-    <row r="4" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="9">
+    <row r="4" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="34">
         <f>A3+1</f>
         <v>2</v>
       </c>
-      <c r="B4" s="10" t="s">
-        <v>33</v>
-      </c>
-      <c r="C4" s="11" t="s">
+      <c r="B4" s="29" t="s">
+        <v>31</v>
+      </c>
+      <c r="C4" s="40" t="s">
+        <v>9</v>
+      </c>
+      <c r="D4" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="D4" s="12" t="s">
-        <v>11</v>
-      </c>
-      <c r="E4" s="12" t="s">
-        <v>9</v>
-      </c>
-      <c r="F4" s="12" t="s">
-        <v>9</v>
-      </c>
-      <c r="G4" s="12" t="s">
-        <v>12</v>
-      </c>
-      <c r="H4" s="13"/>
-      <c r="I4" s="12" t="s">
-        <v>9</v>
-      </c>
-      <c r="J4" s="14">
+      <c r="E4" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="F4" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="G4" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="H4" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="I4" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="J4" s="5">
         <v>1</v>
       </c>
-      <c r="K4" s="13">
+      <c r="K4" s="4">
         <f t="shared" ref="K4:K5" si="0">J4*5</f>
         <v>5</v>
       </c>
-      <c r="L4" s="15" t="s">
-        <v>34</v>
-      </c>
-      <c r="M4" s="38">
+      <c r="L4" s="4"/>
+      <c r="M4" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="N4" s="24">
         <v>0</v>
       </c>
-      <c r="N4" s="16">
-        <f t="shared" ref="N4:N5" si="1">M4*J4</f>
+      <c r="O4" s="7">
+        <f>N4*J4</f>
         <v>0</v>
       </c>
-      <c r="O4" s="38">
+      <c r="P4" s="24">
         <v>0</v>
       </c>
-      <c r="P4" s="16">
-        <f t="shared" ref="P4:P5" si="2">O4*K4</f>
+      <c r="Q4" s="7">
+        <f>P4*K4</f>
         <v>0</v>
       </c>
-      <c r="Q4" s="39" t="s">
-        <v>35</v>
+      <c r="R4" s="36"/>
+      <c r="S4" s="36"/>
+      <c r="T4" s="25" t="s">
+        <v>33</v>
       </c>
     </row>
-    <row r="5" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="7">
+    <row r="5" spans="1:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="33">
         <f>A4+1</f>
         <v>3</v>
       </c>
-      <c r="B5" s="8"/>
-      <c r="C5" s="25" t="s">
+      <c r="B5" s="30"/>
+      <c r="C5" s="41" t="s">
+        <v>11</v>
+      </c>
+      <c r="D5" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="E5" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="D5" s="26" t="s">
-        <v>14</v>
-      </c>
-      <c r="E5" s="26" t="s">
-        <v>15</v>
-      </c>
-      <c r="F5" s="26" t="s">
-        <v>15</v>
-      </c>
-      <c r="G5" s="26" t="s">
-        <v>12</v>
-      </c>
-      <c r="H5" s="27"/>
-      <c r="I5" s="26" t="s">
+      <c r="F5" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="J5" s="28">
+      <c r="G5" s="17" t="s">
+        <v>40</v>
+      </c>
+      <c r="H5" s="17" t="s">
+        <v>40</v>
+      </c>
+      <c r="I5" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="J5" s="16">
         <v>1</v>
       </c>
-      <c r="K5" s="27">
+      <c r="K5" s="15">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="L5" s="29" t="s">
+      <c r="L5" s="15"/>
+      <c r="M5" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="N5" s="20">
+        <v>0</v>
+      </c>
+      <c r="O5" s="22">
+        <f>N5*J5</f>
+        <v>0</v>
+      </c>
+      <c r="P5" s="23">
+        <v>0</v>
+      </c>
+      <c r="Q5" s="22">
+        <f>P5*K5</f>
+        <v>0</v>
+      </c>
+      <c r="R5" s="37"/>
+      <c r="S5" s="37"/>
+      <c r="T5" s="18" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="6" spans="1:20" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="J6" s="31" t="s">
         <v>34</v>
-      </c>
-      <c r="M5" s="34">
-        <v>0</v>
-      </c>
-      <c r="N5" s="36">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="O5" s="37">
-        <v>0</v>
-      </c>
-      <c r="P5" s="36">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="Q5" s="30" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="6" spans="1:17" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="J6" s="31" t="s">
-        <v>36</v>
       </c>
       <c r="K6" s="31"/>
       <c r="L6" s="31"/>
       <c r="M6" s="31"/>
-      <c r="N6" s="6"/>
-      <c r="O6" s="6"/>
-      <c r="P6" s="35">
-        <f>SUM(P3:P5)</f>
+      <c r="N6" s="31"/>
+      <c r="O6" s="3"/>
+      <c r="P6" s="3"/>
+      <c r="Q6" s="21">
+        <f>SUM(Q3:Q5)</f>
         <v>0.56000000000000005</v>
       </c>
+      <c r="R6" s="21"/>
+      <c r="S6" s="21"/>
     </row>
-    <row r="7" spans="1:17" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="J7" s="32" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="K7" s="32"/>
       <c r="L7" s="32"/>
       <c r="M7" s="32"/>
-      <c r="N7" s="35">
-        <f>SUM(N3:N5)</f>
+      <c r="N7" s="32"/>
+      <c r="O7" s="21">
+        <f>SUM(O3:O5)</f>
         <v>0.2</v>
       </c>
-      <c r="O7" s="6"/>
-      <c r="P7" s="35">
-        <f>P6/5</f>
+      <c r="P7" s="3"/>
+      <c r="Q7" s="21">
+        <f>Q6/5</f>
         <v>0.11200000000000002</v>
       </c>
+      <c r="R7" s="21"/>
+      <c r="S7" s="21"/>
     </row>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="A1:Q1"/>
+    <mergeCell ref="A1:T1"/>
     <mergeCell ref="B4:B5"/>
-    <mergeCell ref="J6:M6"/>
-    <mergeCell ref="J7:M7"/>
+    <mergeCell ref="J6:N6"/>
+    <mergeCell ref="J7:N7"/>
   </mergeCells>
-  <conditionalFormatting sqref="N7:P7">
+  <conditionalFormatting sqref="O7:S7">
     <cfRule type="dataBar" priority="4">
       <dataBar>
         <cfvo type="min"/>
@@ -1214,19 +1323,7 @@
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J3:K5">
-    <cfRule type="colorScale" priority="3">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="N3:N5">
+  <conditionalFormatting sqref="O3:O5">
     <cfRule type="dataBar" priority="2">
       <dataBar>
         <cfvo type="min"/>
@@ -1240,7 +1337,7 @@
       </extLst>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P3:P5">
+  <conditionalFormatting sqref="Q3:S5">
     <cfRule type="dataBar" priority="1">
       <dataBar>
         <cfvo type="min"/>
@@ -1254,8 +1351,20 @@
       </extLst>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="J3:L5">
+    <cfRule type="colorScale" priority="5">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
   <hyperlinks>
-    <hyperlink ref="L3" r:id="rId1"/>
+    <hyperlink ref="M3" r:id="rId1"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId2"/>
@@ -1273,7 +1382,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>N7:P7</xm:sqref>
+          <xm:sqref>O7:S7</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="dataBar" id="{1F3C9499-BAF5-480E-B6DC-C251739A2329}">
@@ -1286,7 +1395,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>N3:N5</xm:sqref>
+          <xm:sqref>O3:O5</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="dataBar" id="{BEF2DB92-627B-47B5-95B1-BC0A89D36722}">
@@ -1299,7 +1408,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>P3:P5</xm:sqref>
+          <xm:sqref>Q3:S5</xm:sqref>
         </x14:conditionalFormatting>
       </x14:conditionalFormattings>
     </ext>
